--- a/cet4/result/55_重生钢琴_音乐才女的逆袭/55_重生钢琴_音乐才女的逆袭_学习版.xlsx
+++ b/cet4/result/55_重生钢琴_音乐才女的逆袭/55_重生钢琴_音乐才女的逆袭_学习版.xlsx
@@ -397,619 +397,493 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D34"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>crack</v>
       </c>
       <c r="B2" t="str">
-        <v>crack</v>
+        <v>/kræk/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./v./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>裂缝</v>
       </c>
-      <c r="D2" t="str">
-        <v>crack(裂缝)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>scar</v>
       </c>
       <c r="B3" t="str">
-        <v>scar</v>
+        <v>/skɑːr/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D3" t="str">
         <v>伤痕</v>
       </c>
-      <c r="D3" t="str">
-        <v>scar(伤痕)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>rose</v>
       </c>
       <c r="B4" t="str">
-        <v>rose</v>
+        <v>/roʊz/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>玫瑰</v>
       </c>
-      <c r="D4" t="str">
-        <v>rose(玫瑰)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>racial</v>
       </c>
       <c r="B5" t="str">
-        <v>racial</v>
+        <v>/ˈreɪʃl/</v>
       </c>
       <c r="C5" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D5" t="str">
         <v>种族的</v>
       </c>
-      <c r="D5" t="str">
-        <v>racial(种族的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>grow</v>
       </c>
       <c r="B6" t="str">
-        <v>grow</v>
+        <v>/ɡroʊ/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>生长</v>
       </c>
-      <c r="D6" t="str">
-        <v>grow(生长)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>should</v>
       </c>
       <c r="B7" t="str">
-        <v>should</v>
+        <v>/ʃəd,ʃʊd/</v>
       </c>
       <c r="C7" t="str">
+        <v>aux.</v>
+      </c>
+      <c r="D7" t="str">
         <v>应该</v>
       </c>
-      <c r="D7" t="str">
-        <v>should(应该)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>fragment</v>
       </c>
       <c r="B8" t="str">
-        <v>fragment</v>
+        <v>/ˈfræɡmənt;  fræɡˈment/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>碎片</v>
       </c>
-      <c r="D8" t="str">
-        <v>fragment(碎片)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>attack</v>
       </c>
       <c r="B9" t="str">
-        <v>attack</v>
+        <v>/əˈtæk/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>攻击</v>
       </c>
-      <c r="D9" t="str">
-        <v>attack(攻击)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>brand</v>
       </c>
       <c r="B10" t="str">
-        <v>brand</v>
+        <v>/brænd/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D10" t="str">
         <v>品牌</v>
       </c>
-      <c r="D10" t="str">
-        <v>brand(品牌)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>torrent</v>
       </c>
       <c r="B11" t="str">
-        <v>torrent</v>
+        <v>/ˈtɔːrənt/</v>
       </c>
       <c r="C11" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D11" t="str">
         <v>急流</v>
       </c>
-      <c r="D11" t="str">
-        <v>torrent(急流)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>downstairs</v>
       </c>
       <c r="B12" t="str">
-        <v>downstairs</v>
+        <v>/ˌdaʊnˈsterz/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D12" t="str">
         <v>楼下</v>
       </c>
-      <c r="D12" t="str">
-        <v>downstairs(楼下)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>try</v>
       </c>
       <c r="B13" t="str">
-        <v>try</v>
+        <v>/traɪ/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D13" t="str">
         <v>尝试</v>
       </c>
-      <c r="D13" t="str">
-        <v>try(尝试)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>training</v>
       </c>
       <c r="B14" t="str">
-        <v>training</v>
+        <v>/ˈtreɪnɪŋ/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v.</v>
+      </c>
+      <c r="D14" t="str">
         <v>训练</v>
       </c>
-      <c r="D14" t="str">
-        <v>training(训练)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>deepen</v>
       </c>
       <c r="B15" t="str">
-        <v>deepen</v>
+        <v>/ˈdiːpən/</v>
       </c>
       <c r="C15" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D15" t="str">
         <v>加深</v>
       </c>
-      <c r="D15" t="str">
-        <v>deepen(加深)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>era</v>
       </c>
       <c r="B16" t="str">
-        <v>era</v>
+        <v>/ˈɪrə,ˈerə/</v>
       </c>
       <c r="C16" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D16" t="str">
         <v>时代</v>
       </c>
-      <c r="D16" t="str">
-        <v>era(时代)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>exaggerate</v>
       </c>
       <c r="B17" t="str">
-        <v>exaggerate</v>
+        <v>/ɪɡˈzædʒəreɪt/</v>
       </c>
       <c r="C17" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D17" t="str">
         <v>夸大</v>
       </c>
-      <c r="D17" t="str">
-        <v>exaggerate(夸大)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>depth</v>
       </c>
       <c r="B18" t="str">
-        <v>depth</v>
+        <v>/depθ/</v>
       </c>
       <c r="C18" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D18" t="str">
         <v>深度</v>
       </c>
-      <c r="D18" t="str">
-        <v>depth(深度)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>polish</v>
       </c>
       <c r="B19" t="str">
-        <v>polish</v>
+        <v>/ˈpɑːlɪʃ/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D19" t="str">
         <v>光泽</v>
       </c>
-      <c r="D19" t="str">
-        <v>polish(光泽)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>headmaster</v>
       </c>
       <c r="B20" t="str">
-        <v>headmaster</v>
+        <v>/ˌhedˈmæstər/</v>
       </c>
       <c r="C20" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D20" t="str">
         <v>校长</v>
       </c>
-      <c r="D20" t="str">
-        <v>headmaster(校长)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>crystal</v>
       </c>
       <c r="B21" t="str">
-        <v>rose</v>
+        <v>/ˈkrɪstl/</v>
       </c>
       <c r="C21" t="str">
-        <v>玫瑰</v>
+        <v>n./adj.</v>
       </c>
       <c r="D21" t="str">
-        <v>rose(玫瑰)📢</v>
+        <v>水晶</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>gracious</v>
       </c>
       <c r="B22" t="str">
-        <v>crystal</v>
+        <v>/ˈɡreɪʃəs/</v>
       </c>
       <c r="C22" t="str">
-        <v>水晶</v>
+        <v>adj./int.</v>
       </c>
       <c r="D22" t="str">
-        <v>crystal(水晶)📢</v>
+        <v>亲切的</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>hence</v>
       </c>
       <c r="B23" t="str">
-        <v>gracious</v>
+        <v>/hens/</v>
       </c>
       <c r="C23" t="str">
-        <v>亲切的</v>
+        <v>v./adv.</v>
       </c>
       <c r="D23" t="str">
-        <v>gracious(亲切的)📢</v>
+        <v>因此</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>widen</v>
       </c>
       <c r="B24" t="str">
-        <v>hence</v>
+        <v>/ˈwaɪdn/</v>
       </c>
       <c r="C24" t="str">
-        <v>因此</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D24" t="str">
-        <v>hence(因此)📢</v>
+        <v>扩大</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>chair</v>
       </c>
       <c r="B25" t="str">
-        <v>widen</v>
+        <v>/tʃer/</v>
       </c>
       <c r="C25" t="str">
-        <v>扩大</v>
+        <v>n./vt.</v>
       </c>
       <c r="D25" t="str">
-        <v>widen(扩大)📢</v>
+        <v>椅子</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>invest</v>
       </c>
       <c r="B26" t="str">
-        <v>chair</v>
+        <v>/ɪnˈvest/</v>
       </c>
       <c r="C26" t="str">
-        <v>椅子</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>chair(椅子)📢</v>
+        <v>投资</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>waterproof</v>
       </c>
       <c r="B27" t="str">
-        <v>invest</v>
+        <v>/ˈwɔːtərpruːf/</v>
       </c>
       <c r="C27" t="str">
-        <v>投资</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>invest(投资)📢</v>
+        <v>防水</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>sharpen</v>
       </c>
       <c r="B28" t="str">
-        <v>waterproof</v>
+        <v>/ˈʃɑːrpən/</v>
       </c>
       <c r="C28" t="str">
-        <v>防水</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D28" t="str">
-        <v>waterproof(防水)📢</v>
+        <v>磨快</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>pillow</v>
       </c>
       <c r="B29" t="str">
-        <v>gracious</v>
+        <v>/ˈpɪloʊ/</v>
       </c>
       <c r="C29" t="str">
-        <v>亲切的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>gracious(亲切的)📢</v>
+        <v>枕头</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>ahead</v>
       </c>
       <c r="B30" t="str">
-        <v>brand</v>
+        <v>/əˈhed/</v>
       </c>
       <c r="C30" t="str">
-        <v>品牌</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D30" t="str">
-        <v>brand(品牌)📢</v>
+        <v>向前</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>colony</v>
       </c>
       <c r="B31" t="str">
-        <v>sharpen</v>
+        <v>/ˈkɑːləni/</v>
       </c>
       <c r="C31" t="str">
-        <v>磨快</v>
+        <v>n.</v>
       </c>
       <c r="D31" t="str">
-        <v>sharpen(磨快)📢</v>
+        <v>殖民地</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>dramatic</v>
       </c>
       <c r="B32" t="str">
-        <v>pillow</v>
+        <v>/drəˈmætɪk/</v>
       </c>
       <c r="C32" t="str">
-        <v>枕头</v>
+        <v>adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>pillow(枕头)📢</v>
+        <v>戏剧性的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>pleasure</v>
       </c>
       <c r="B33" t="str">
-        <v>ahead</v>
+        <v>/ˈpleʒər/</v>
       </c>
       <c r="C33" t="str">
-        <v>向前</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>ahead(向前)📢</v>
+        <v>快乐</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>end</v>
       </c>
       <c r="B34" t="str">
-        <v>colony</v>
+        <v>/end/</v>
       </c>
       <c r="C34" t="str">
-        <v>殖民地</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>colony(殖民地)📢</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35" t="str">
-        <v>dramatic</v>
-      </c>
-      <c r="C35" t="str">
-        <v>戏剧性的</v>
-      </c>
-      <c r="D35" t="str">
-        <v>dramatic(戏剧性的)📢</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36" t="str">
-        <v>torrent</v>
-      </c>
-      <c r="C36" t="str">
-        <v>急流</v>
-      </c>
-      <c r="D36" t="str">
-        <v>torrent(急流)📢</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37" t="str">
-        <v>pleasure</v>
-      </c>
-      <c r="C37" t="str">
-        <v>快乐</v>
-      </c>
-      <c r="D37" t="str">
-        <v>pleasure(快乐)📢</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="str">
-        <v>headmaster</v>
-      </c>
-      <c r="C38" t="str">
-        <v>校长</v>
-      </c>
-      <c r="D38" t="str">
-        <v>headmaster(校长)📢</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39" t="str">
-        <v>headmaster</v>
-      </c>
-      <c r="C39" t="str">
-        <v>校长</v>
-      </c>
-      <c r="D39" t="str">
-        <v>headmaster(校长)📢</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40" t="str">
-        <v>rose</v>
-      </c>
-      <c r="C40" t="str">
-        <v>玫瑰</v>
-      </c>
-      <c r="D40" t="str">
-        <v>rose(玫瑰)📢</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41" t="str">
-        <v>end</v>
-      </c>
-      <c r="C41" t="str">
         <v>结束</v>
-      </c>
-      <c r="D41" t="str">
-        <v>end(结束)📢</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42" t="str">
-        <v>pleasure</v>
-      </c>
-      <c r="C42" t="str">
-        <v>快乐</v>
-      </c>
-      <c r="D42" t="str">
-        <v>pleasure(快乐)📢</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43" t="str">
-        <v>era</v>
-      </c>
-      <c r="C43" t="str">
-        <v>时代</v>
-      </c>
-      <c r="D43" t="str">
-        <v>era(时代)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D34"/>
   </ignoredErrors>
 </worksheet>
 </file>